--- a/Шаблон Excel.xlsx
+++ b/Шаблон Excel.xlsx
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dviktorov\Desktop\Project\Plugins\Addon manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAF03D1-9C01-4FCE-9512-665A82C29947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28899061-973B-488F-BA25-88483AFEE8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Наборы для матриц" sheetId="1" r:id="rId1"/>
     <sheet name="Матрица" sheetId="2" r:id="rId2"/>
     <sheet name="Параметры" sheetId="3" r:id="rId3"/>
     <sheet name="Адаптер" sheetId="4" r:id="rId4"/>
-    <sheet name="Адаптер1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
   <si>
     <t>Имя набора</t>
   </si>
@@ -143,48 +142,15 @@
     <t>Раздел КР - Стадия Р</t>
   </si>
   <si>
-    <t>Шпунтовое ограждение котлована</t>
-  </si>
-  <si>
-    <t>Фундамент несущей конструкции</t>
-  </si>
-  <si>
-    <t>IfcPile</t>
-  </si>
-  <si>
-    <t>НЦ.ОК.1, НЦ.ОК.2, НЦ.ОК.3</t>
-  </si>
-  <si>
-    <t>Ограждение котлована из шпунта Ларсена; Ограждение котлована из стальных труб; Ограждение котлована из свай</t>
-  </si>
-  <si>
     <t>+</t>
   </si>
   <si>
-    <t>Распорная система</t>
-  </si>
-  <si>
-    <t>Каркас несущий, Несущие колонны</t>
-  </si>
-  <si>
-    <t>НЦ.ОК.4</t>
-  </si>
-  <si>
     <t>Распорная система ограждения котлована</t>
   </si>
   <si>
     <t>Стена в грунте</t>
   </si>
   <si>
-    <t>Стены</t>
-  </si>
-  <si>
-    <t>IfcFooting</t>
-  </si>
-  <si>
-    <t>НЦ.ОК.5</t>
-  </si>
-  <si>
     <t>Укажите группу параметров:</t>
   </si>
   <si>
@@ -236,34 +202,99 @@
     <t>Этаж_12</t>
   </si>
   <si>
-    <t>DIMA</t>
-  </si>
-  <si>
-    <t>Комплект_документации1</t>
-  </si>
-  <si>
-    <t>Этаж1</t>
-  </si>
-  <si>
-    <t>Этаж_1</t>
-  </si>
-  <si>
-    <t>Секция1</t>
-  </si>
-  <si>
-    <t>Корпус1</t>
+    <t>03.04_Горизонтальные ж/б конструкции</t>
+  </si>
+  <si>
+    <t>03.04.01.01_Перекрытия ж/б монолитные</t>
+  </si>
+  <si>
+    <t>03.04.01.01</t>
+  </si>
+  <si>
+    <t>03.04.01.02_Балки ж/б монолитные</t>
+  </si>
+  <si>
+    <t>03.04.01.02</t>
+  </si>
+  <si>
+    <t>03.04.01.03_Лестницы ж/б монолитные</t>
+  </si>
+  <si>
+    <t>03.04.01.03.01, 03.04.01.03.02</t>
+  </si>
+  <si>
+    <t>03.05_Металлические конструкции</t>
+  </si>
+  <si>
+    <t>03.05.01_Металлические конструкции несущие</t>
+  </si>
+  <si>
+    <t>03.05.01.01, 03.05.01.03, 03.05.01.04</t>
+  </si>
+  <si>
+    <t>03.05.02_Металлические ограждения и поручни</t>
+  </si>
+  <si>
+    <t>03.05.02</t>
+  </si>
+  <si>
+    <t>Лестницы</t>
+  </si>
+  <si>
+    <t>IfcStair</t>
+  </si>
+  <si>
+    <t>IfcRailing</t>
+  </si>
+  <si>
+    <t>IfcSlab</t>
+  </si>
+  <si>
+    <t>Плита перекрытия железобетонная монолитная</t>
+  </si>
+  <si>
+    <t>IfcBeam</t>
+  </si>
+  <si>
+    <t>Каркас несущий</t>
+  </si>
+  <si>
+    <t>Перекрытия</t>
+  </si>
+  <si>
+    <t>Каркас несущий; Несущие колонны</t>
+  </si>
+  <si>
+    <t>Ограждения</t>
+  </si>
+  <si>
+    <t>Ограждение металлическое, поручень (перила)</t>
+  </si>
+  <si>
+    <t>Несущие металлические конструкции</t>
+  </si>
+  <si>
+    <t>IfcBeam, IfcColumn, IfcMember</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,8 +313,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Tahoma"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,8 +371,20 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -359,78 +407,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{0ED6E52B-D732-4CF0-ADB6-CD467483F20F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -801,23 +933,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="17" t="s">
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="18"/>
+      <c r="G1" s="27"/>
     </row>
     <row r="2" spans="1:7" ht="90.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
       <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
@@ -835,8 +967,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
@@ -928,10 +1060,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
@@ -955,13 +1087,13 @@
       <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -986,114 +1118,229 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-    </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="32"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>44</v>
-      </c>
+      <c r="F7" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1119,10 +1366,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -1131,22 +1378,22 @@
     </row>
     <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1154,16 +1401,16 @@
         <v>33</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>33</v>
@@ -1174,10 +1421,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1187,13 +1434,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -1206,10 +1453,10 @@
         <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1219,13 +1466,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1236,138 +1483,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9234C89-8F3A-4DCE-BCAE-74884399A3A5}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Шаблон Excel.xlsx
+++ b/Шаблон Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dviktorov\Desktop\Project\Plugins\Addon manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28899061-973B-488F-BA25-88483AFEE8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE88E319-05F6-48AA-921B-9E3C4CEA8AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="96">
   <si>
     <t>Имя набора</t>
   </si>
@@ -145,12 +145,6 @@
     <t>+</t>
   </si>
   <si>
-    <t>Распорная система ограждения котлована</t>
-  </si>
-  <si>
-    <t>Стена в грунте</t>
-  </si>
-  <si>
     <t>Укажите группу параметров:</t>
   </si>
   <si>
@@ -202,79 +196,121 @@
     <t>Этаж_12</t>
   </si>
   <si>
-    <t>03.04_Горизонтальные ж/б конструкции</t>
-  </si>
-  <si>
-    <t>03.04.01.01_Перекрытия ж/б монолитные</t>
-  </si>
-  <si>
-    <t>03.04.01.01</t>
-  </si>
-  <si>
-    <t>03.04.01.02_Балки ж/б монолитные</t>
-  </si>
-  <si>
-    <t>03.04.01.02</t>
-  </si>
-  <si>
-    <t>03.04.01.03_Лестницы ж/б монолитные</t>
-  </si>
-  <si>
-    <t>03.04.01.03.01, 03.04.01.03.02</t>
-  </si>
-  <si>
-    <t>03.05_Металлические конструкции</t>
-  </si>
-  <si>
-    <t>03.05.01_Металлические конструкции несущие</t>
-  </si>
-  <si>
-    <t>03.05.01.01, 03.05.01.03, 03.05.01.04</t>
-  </si>
-  <si>
-    <t>03.05.02_Металлические ограждения и поручни</t>
-  </si>
-  <si>
-    <t>03.05.02</t>
-  </si>
-  <si>
-    <t>Лестницы</t>
-  </si>
-  <si>
-    <t>IfcStair</t>
-  </si>
-  <si>
-    <t>IfcRailing</t>
-  </si>
-  <si>
-    <t>IfcSlab</t>
-  </si>
-  <si>
-    <t>Плита перекрытия железобетонная монолитная</t>
-  </si>
-  <si>
-    <t>IfcBeam</t>
-  </si>
-  <si>
-    <t>Каркас несущий</t>
-  </si>
-  <si>
-    <t>Перекрытия</t>
-  </si>
-  <si>
-    <t>Каркас несущий; Несущие колонны</t>
-  </si>
-  <si>
-    <t>Ограждения</t>
-  </si>
-  <si>
-    <t>Ограждение металлическое, поручень (перила)</t>
-  </si>
-  <si>
-    <t>Несущие металлические конструкции</t>
-  </si>
-  <si>
-    <t>IfcBeam, IfcColumn, IfcMember</t>
+    <t>03_Конструкции строений</t>
+  </si>
+  <si>
+    <t>04.02_Системы вентиляции</t>
+  </si>
+  <si>
+    <t>03.01_Фундамент ж/б</t>
+  </si>
+  <si>
+    <t>03.01.01.01_Фундаментная плита монолитная</t>
+  </si>
+  <si>
+    <t>03.03_Вертикальные ж/б конструкции</t>
+  </si>
+  <si>
+    <t>03.03.01.01_Стены ж/б монолитные</t>
+  </si>
+  <si>
+    <t>03.03.01.03_Колонны ж/б монолитные</t>
+  </si>
+  <si>
+    <t>04_Инженерные сети</t>
+  </si>
+  <si>
+    <t>04.02.01_Воздуховоды</t>
+  </si>
+  <si>
+    <t>04.02.01.01, 04.02.01.02, 04.02.01.07</t>
+  </si>
+  <si>
+    <t>04.02.03_Материалы изоляции воздуховодов</t>
+  </si>
+  <si>
+    <t>04.02.03.01</t>
+  </si>
+  <si>
+    <t>04.02.04_Воздухораспределительные устройства</t>
+  </si>
+  <si>
+    <t>04.02.04.03, 04.02.04.04</t>
+  </si>
+  <si>
+    <t>04.02.05_Арматура воздуховодов</t>
+  </si>
+  <si>
+    <t>04.02.05.01, 04.02.05.03, 04.02.05.05</t>
+  </si>
+  <si>
+    <t>03.01.01.01</t>
+  </si>
+  <si>
+    <t>03.03.01.01</t>
+  </si>
+  <si>
+    <t>03.03.01.03</t>
+  </si>
+  <si>
+    <t>IfcFooting</t>
+  </si>
+  <si>
+    <t>Фундамент несущей конструкции</t>
+  </si>
+  <si>
+    <t>Стены</t>
+  </si>
+  <si>
+    <t>IfcWall</t>
+  </si>
+  <si>
+    <t>Несущие колонны</t>
+  </si>
+  <si>
+    <t>IfcColumn</t>
+  </si>
+  <si>
+    <t>Воздуховоды</t>
+  </si>
+  <si>
+    <t>IfcDuctSegment</t>
+  </si>
+  <si>
+    <t>Изоляция воздуховодов</t>
+  </si>
+  <si>
+    <t>IfcCovering</t>
+  </si>
+  <si>
+    <t>Воздухораспределители</t>
+  </si>
+  <si>
+    <t>IfcAirTerminal</t>
+  </si>
+  <si>
+    <t>Арматура воздуховодов</t>
+  </si>
+  <si>
+    <t>IfcDuctFitting</t>
+  </si>
+  <si>
+    <t>Изоляционные материалы для воздуховодов</t>
+  </si>
+  <si>
+    <t>Фундаментная плита железобетонная монолитная</t>
+  </si>
+  <si>
+    <t>Стена железобетонная монолитная</t>
+  </si>
+  <si>
+    <t>Воздуховоды систем вентиляции</t>
+  </si>
+  <si>
+    <t>Воздухораспределительные устройства</t>
+  </si>
+  <si>
+    <t>Колонна железобетонная монолитная</t>
   </si>
 </sst>
 </file>
@@ -299,27 +335,34 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Tahoma"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,8 +426,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -439,24 +488,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -467,102 +498,120 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{0ED6E52B-D732-4CF0-ADB6-CD467483F20F}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{AC527096-C4D7-4AFB-B5D4-3B0A53A9BDE1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -863,57 +912,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="1" max="1" width="32" style="3" customWidth="1"/>
+    <col min="2" max="2" width="90" style="3" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -925,126 +975,127 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="7" width="5" customWidth="1"/>
+    <col min="1" max="1" width="8" style="3" customWidth="1"/>
+    <col min="2" max="2" width="36" style="3" customWidth="1"/>
+    <col min="3" max="7" width="5" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="26" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" spans="1:7" ht="90.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="5" t="s">
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" ht="90.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="4" t="s">
+    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="12" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1060,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.42578125" customWidth="1"/>
@@ -1071,281 +1122,360 @@
     <col min="6" max="10" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-    </row>
-    <row r="2" spans="1:10" ht="180" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="11" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:11" ht="180" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:11" s="40" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="32"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B6" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C8" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="21" t="s">
+      <c r="E8" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="E9" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="B15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
+      <c r="E15" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1354,129 +1484,130 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="1" max="1" width="32" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14" style="3" customWidth="1"/>
+    <col min="3" max="3" width="50" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B2" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="C2" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="D2" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="F2" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="15" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="C3" s="32" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="D3" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="16" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
